--- a/data/trans_dic/P04D$notiene-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P04D$notiene-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tiene calefacción ni aparatos de calefacción en su vivienda</t>
+          <t>Población que no tiene calefacción ni aparatos de calefacción en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,67; 18,82</t>
+          <t>10,69; 19,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,84; 55,84</t>
+          <t>43,38; 55,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,41; 24,92</t>
+          <t>13,42; 24,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,22; 24,29</t>
+          <t>14,79; 24,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,41; 50,06</t>
+          <t>38,9; 50,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,99; 24,06</t>
+          <t>14,86; 23,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,76; 20,25</t>
+          <t>13,62; 20,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,92; 51,4</t>
+          <t>43,07; 51,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,31; 22,45</t>
+          <t>15,0; 22,16</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,67; 11,15</t>
+          <t>5,89; 11,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,4; 31,45</t>
+          <t>23,26; 31,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,83; 15,15</t>
+          <t>7,73; 14,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,2; 11,58</t>
+          <t>6,44; 11,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,24; 26,86</t>
+          <t>19,44; 26,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,79; 13,61</t>
+          <t>8,88; 13,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,69; 10,18</t>
+          <t>6,73; 10,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,24; 27,88</t>
+          <t>22,37; 27,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,07; 13,39</t>
+          <t>9,13; 13,33</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,35</t>
+          <t>0,29; 2,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,72</t>
+          <t>0,87; 3,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,16</t>
+          <t>2,04; 6,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,69</t>
+          <t>0,29; 2,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,36</t>
+          <t>0,26; 2,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,75</t>
+          <t>1,2; 3,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,96</t>
+          <t>0,32; 1,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,4</t>
+          <t>0,68; 2,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,37</t>
+          <t>1,9; 4,38</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,49</t>
+          <t>1,14; 6,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,54</t>
+          <t>2,22; 6,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 7,6</t>
+          <t>1,59; 7,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,74</t>
+          <t>1,32; 4,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,03; 7,57</t>
+          <t>2,83; 7,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,78; 52,38</t>
+          <t>3,91; 50,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,44</t>
+          <t>1,55; 4,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,23</t>
+          <t>3,14; 6,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 38,18</t>
+          <t>3,86; 36,6</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 8,16</t>
+          <t>2,03; 8,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,2</t>
+          <t>0,43; 3,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,25</t>
+          <t>0,09; 2,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 9,61</t>
+          <t>3,22; 9,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,79</t>
+          <t>0,83; 4,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 7,56</t>
+          <t>3,27; 7,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,32</t>
+          <t>0,87; 3,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,1</t>
+          <t>0,12; 1,11</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 2,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,93; 40,86</t>
+          <t>29,55; 41,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,06</t>
+          <t>0,67; 4,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,93; 40,82</t>
+          <t>28,85; 40,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,87</t>
+          <t>1,08; 3,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,61</t>
+          <t>0,18; 1,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30,58; 38,68</t>
+          <t>30,38; 39,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,4</t>
+          <t>1,1; 3,43</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,06</t>
+          <t>0,96; 3,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,87; 23,2</t>
+          <t>16,86; 23,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28,03; 37,11</t>
+          <t>28,16; 36,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,11</t>
+          <t>1,45; 3,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,83; 23,08</t>
+          <t>16,71; 23,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,9; 34,53</t>
+          <t>10,04; 34,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,98</t>
+          <t>1,41; 3,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,84; 22,62</t>
+          <t>17,85; 22,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,96; 34,1</t>
+          <t>17,87; 34,17</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,33</t>
+          <t>1,87; 4,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,54</t>
+          <t>0,26; 1,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,19</t>
+          <t>0,67; 3,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,92</t>
+          <t>1,0; 2,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,93</t>
+          <t>0,49; 2,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,66</t>
+          <t>1,65; 3,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,3</t>
+          <t>1,67; 3,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,44</t>
+          <t>0,48; 1,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,87</t>
+          <t>1,18; 2,91</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,42; 4,89</t>
+          <t>3,43; 4,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14,4; 17,1</t>
+          <t>14,5; 17,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,0; 11,96</t>
+          <t>8,32; 11,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,76; 5,19</t>
+          <t>3,82; 5,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,35; 15,83</t>
+          <t>13,45; 15,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,82; 17,32</t>
+          <t>9,68; 17,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,87; 4,84</t>
+          <t>3,83; 4,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,18; 15,97</t>
+          <t>14,21; 16,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,82; 14,13</t>
+          <t>9,82; 14,18</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no tiene calefacción ni aparatos de calefacción en su vivienda</t>
+          <t>Población que no tiene calefacción ni aparatos de calefacción en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31253; 55119</t>
+          <t>31321; 56300</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>125834; 164036</t>
+          <t>127434; 162962</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41760; 77618</t>
+          <t>41792; 77547</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40681; 69491</t>
+          <t>42324; 68962</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>110902; 144513</t>
+          <t>112301; 145899</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43407; 69672</t>
+          <t>43041; 67128</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>79657; 117273</t>
+          <t>78871; 117019</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>249999; 299368</t>
+          <t>250892; 299411</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>92007; 134939</t>
+          <t>90161; 133184</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28567; 56143</t>
+          <t>29674; 57006</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>117588; 158070</t>
+          <t>116879; 156324</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40595; 78546</t>
+          <t>40053; 75469</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32322; 60383</t>
+          <t>33587; 61937</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>100627; 140486</t>
+          <t>101698; 139940</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45277; 70082</t>
+          <t>45714; 69841</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68569; 104346</t>
+          <t>68992; 106207</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>228066; 285966</t>
+          <t>229487; 284834</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93685; 138316</t>
+          <t>94371; 137696</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>940; 7601</t>
+          <t>935; 7775</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2740; 11855</t>
+          <t>2756; 12629</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5467; 19396</t>
+          <t>6429; 19622</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>982; 9157</t>
+          <t>984; 8335</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>894; 7944</t>
+          <t>884; 8587</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4013; 13040</t>
+          <t>4177; 12929</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2844; 13059</t>
+          <t>2128; 12246</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4641; 15745</t>
+          <t>4426; 15659</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12041; 28980</t>
+          <t>12608; 29031</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3940; 20472</t>
+          <t>4266; 22378</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8595; 24196</t>
+          <t>8225; 23492</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4827; 23754</t>
+          <t>4959; 23930</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5110; 18455</t>
+          <t>5134; 18550</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11749; 29336</t>
+          <t>10960; 29391</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17890; 247989</t>
+          <t>18503; 237807</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12180; 33832</t>
+          <t>11779; 33158</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24107; 47176</t>
+          <t>23782; 49334</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28597; 300054</t>
+          <t>30328; 287698</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5094; 17350</t>
+          <t>4326; 17679</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>935; 8866</t>
+          <t>918; 7855</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>161; 4029</t>
+          <t>163; 3880</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7053; 21101</t>
+          <t>7081; 20490</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1765; 10476</t>
+          <t>1814; 10375</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2581</t>
+          <t>0; 2910</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13978; 32657</t>
+          <t>14154; 32562</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3651; 14262</t>
+          <t>3744; 14576</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>523; 4806</t>
+          <t>508; 4867</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5899</t>
+          <t>0; 5937</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>76123; 107524</t>
+          <t>77758; 108592</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1867; 10958</t>
+          <t>1801; 11628</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 7226</t>
+          <t>0; 7551</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>79025; 111497</t>
+          <t>78791; 109750</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2637; 9948</t>
+          <t>2765; 9959</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>972; 8907</t>
+          <t>985; 9046</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>163988; 207409</t>
+          <t>162893; 209508</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6047; 17890</t>
+          <t>5816; 18090</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6259; 20284</t>
+          <t>6359; 19975</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>110782; 152325</t>
+          <t>110703; 155464</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>174152; 230515</t>
+          <t>174960; 229223</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10577; 28512</t>
+          <t>10077; 27060</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>116336; 159569</t>
+          <t>115490; 161868</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>92110; 291900</t>
+          <t>84872; 292670</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18072; 40457</t>
+          <t>19185; 41516</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>240423; 304923</t>
+          <t>240568; 300333</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>278006; 500141</t>
+          <t>262088; 501154</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>14181; 33664</t>
+          <t>14498; 32985</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2039; 11977</t>
+          <t>2051; 12726</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7009; 29512</t>
+          <t>6200; 28746</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8245; 24088</t>
+          <t>8239; 23457</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4123; 15985</t>
+          <t>4013; 16990</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11636; 26302</t>
+          <t>11807; 27242</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26554; 52790</t>
+          <t>26673; 50897</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7487; 23084</t>
+          <t>7699; 23749</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19205; 47225</t>
+          <t>19469; 47893</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>117068; 167283</t>
+          <t>117374; 166824</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>488903; 580562</t>
+          <t>492038; 577072</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>276342; 413108</t>
+          <t>287278; 412953</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>133591; 184342</t>
+          <t>135924; 184531</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>473334; 561205</t>
+          <t>476803; 562513</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>363645; 641776</t>
+          <t>358684; 652698</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>269870; 337742</t>
+          <t>266958; 339684</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>984256; 1108322</t>
+          <t>986040; 1118529</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>703057; 1011512</t>
+          <t>703072; 1014943</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P04D$notiene-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P04D$notiene-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>23,1%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,69; 19,22</t>
+          <t>10,43; 18,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,38; 55,47</t>
+          <t>43,92; 56,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,42; 24,9</t>
+          <t>19,39; 30,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,79; 24,1</t>
+          <t>14,49; 24,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,9; 50,54</t>
+          <t>38,3; 50,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,86; 23,18</t>
+          <t>18,27; 26,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,62; 20,21</t>
+          <t>13,93; 20,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43,07; 51,4</t>
+          <t>42,66; 51,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,0; 22,16</t>
+          <t>20,28; 26,67</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,89; 11,32</t>
+          <t>5,98; 11,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,26; 31,1</t>
+          <t>23,07; 30,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,73; 14,56</t>
+          <t>7,98; 14,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,44; 11,87</t>
+          <t>6,3; 11,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,44; 26,75</t>
+          <t>19,48; 27,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,88; 13,56</t>
+          <t>8,23; 12,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,73; 10,36</t>
+          <t>6,6; 10,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,37; 27,77</t>
+          <t>22,06; 27,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,13; 13,33</t>
+          <t>9,11; 13,45</t>
         </is>
       </c>
     </row>
@@ -855,37 +855,37 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>3,58%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,4</t>
+          <t>0,29; 2,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,96</t>
+          <t>0,86; 3,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 6,23</t>
+          <t>2,48; 7,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,44</t>
+          <t>0,0; 2,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,55</t>
+          <t>0,27; 2,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,72</t>
+          <t>1,74; 4,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,84</t>
+          <t>0,31; 1,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,39</t>
+          <t>0,66; 2,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,38</t>
+          <t>2,42; 5,35</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,0</t>
+          <t>1,16; 5,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,35</t>
+          <t>2,33; 6,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 7,66</t>
+          <t>2,15; 8,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,77</t>
+          <t>1,31; 4,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 7,59</t>
+          <t>2,99; 7,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 50,23</t>
+          <t>3,62; 8,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,35</t>
+          <t>1,62; 4,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,51</t>
+          <t>3,08; 6,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 36,6</t>
+          <t>3,12; 6,79</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 8,31</t>
+          <t>2,11; 8,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,72</t>
+          <t>0,44; 3,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,17</t>
+          <t>0,36; 3,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 9,33</t>
+          <t>3,14; 9,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,75</t>
+          <t>0,84; 4,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,27; 7,53</t>
+          <t>3,17; 7,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,39</t>
+          <t>0,67; 3,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,11</t>
+          <t>0,34; 1,92</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,17</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29,55; 41,27</t>
+          <t>28,71; 39,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,31</t>
+          <t>0,82; 4,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,85; 40,18</t>
+          <t>28,82; 40,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,87</t>
+          <t>1,07; 3,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,64</t>
+          <t>0,18; 1,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30,38; 39,07</t>
+          <t>30,31; 38,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,43</t>
+          <t>1,16; 3,36</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>34,28%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,01</t>
+          <t>0,83; 3,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,86; 23,68</t>
+          <t>17,25; 24,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28,16; 36,9</t>
+          <t>29,54; 37,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,9</t>
+          <t>1,42; 4,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,71; 23,42</t>
+          <t>16,82; 23,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,04; 34,62</t>
+          <t>31,65; 38,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,06</t>
+          <t>1,45; 3,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,85; 22,28</t>
+          <t>17,83; 22,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17,87; 34,17</t>
+          <t>31,67; 36,76</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,25</t>
+          <t>1,9; 4,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,63</t>
+          <t>0,27; 1,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,1</t>
+          <t>1,35; 3,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,85</t>
+          <t>1,11; 2,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,06</t>
+          <t>0,51; 1,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,8</t>
+          <t>1,99; 4,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,18</t>
+          <t>1,57; 3,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,48</t>
+          <t>0,47; 1,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,91</t>
+          <t>1,93; 3,71</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,43; 4,88</t>
+          <t>3,54; 4,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14,5; 17,0</t>
+          <t>14,48; 17,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,32; 11,96</t>
+          <t>11,08; 13,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,82; 5,19</t>
+          <t>3,81; 5,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,45; 15,87</t>
+          <t>13,33; 15,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,68; 17,62</t>
+          <t>11,33; 13,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,83; 4,87</t>
+          <t>3,85; 4,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,21; 16,12</t>
+          <t>14,35; 15,96</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,82; 14,18</t>
+          <t>11,51; 13,09</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56858</t>
+          <t>78378</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52757</t>
+          <t>68293</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>109614</t>
+          <t>146671</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31321; 56300</t>
+          <t>30552; 55093</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>127434; 162962</t>
+          <t>129014; 164654</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41792; 77547</t>
+          <t>61814; 95759</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42324; 68962</t>
+          <t>41458; 69000</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>112301; 145899</t>
+          <t>110585; 145804</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43041; 67128</t>
+          <t>57757; 82590</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>78871; 117019</t>
+          <t>80647; 119060</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>250892; 299411</t>
+          <t>248475; 299129</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>90161; 133184</t>
+          <t>128780; 169340</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>58667</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56546</t>
+          <t>56708</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>113722</t>
+          <t>115375</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29674; 57006</t>
+          <t>30136; 55816</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>116879; 156324</t>
+          <t>115934; 155731</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40053; 75469</t>
+          <t>42343; 79018</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33587; 61937</t>
+          <t>32880; 59667</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>101698; 139940</t>
+          <t>101903; 142481</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45714; 69841</t>
+          <t>44953; 68816</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68992; 106207</t>
+          <t>67699; 105197</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>229487; 284834</t>
+          <t>226234; 284554</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>94371; 137696</t>
+          <t>98114; 144868</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11272</t>
+          <t>13954</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19012</t>
+          <t>23995</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>935; 7775</t>
+          <t>936; 8477</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2756; 12629</t>
+          <t>2745; 12017</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6429; 19622</t>
+          <t>7811; 24130</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>984; 8335</t>
+          <t>0; 8619</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>884; 8587</t>
+          <t>897; 8566</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4177; 12929</t>
+          <t>6194; 16059</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2128; 12246</t>
+          <t>2060; 12211</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4426; 15659</t>
+          <t>4294; 15726</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12608; 29031</t>
+          <t>16193; 35873</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11670</t>
+          <t>15780</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88249</t>
+          <t>22463</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>99919</t>
+          <t>38243</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4266; 22378</t>
+          <t>4310; 21548</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8225; 23492</t>
+          <t>8613; 24998</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4959; 23930</t>
+          <t>8018; 31175</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5134; 18550</t>
+          <t>5098; 18016</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10960; 29391</t>
+          <t>11584; 29824</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18503; 237807</t>
+          <t>15149; 35386</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11779; 33158</t>
+          <t>12332; 33218</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23782; 49334</t>
+          <t>23305; 46610</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30328; 287698</t>
+          <t>24734; 53726</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>880</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>3823</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4326; 17679</t>
+          <t>4480; 17570</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>918; 7855</t>
+          <t>930; 7971</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>163; 3880</t>
+          <t>746; 7931</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7081; 20490</t>
+          <t>6888; 20545</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1814; 10375</t>
+          <t>1841; 10436</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2910</t>
+          <t>0; 2716</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14154; 32562</t>
+          <t>13716; 33360</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3744; 14576</t>
+          <t>2898; 13938</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>508; 4867</t>
+          <t>1465; 8342</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>11078</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5937</t>
+          <t>0; 5867</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>77758; 108592</t>
+          <t>75539; 104992</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1801; 11628</t>
+          <t>2219; 11550</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 7551</t>
+          <t>0; 6923</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>78791; 109750</t>
+          <t>78709; 109913</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2765; 9959</t>
+          <t>2816; 10298</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>985; 9046</t>
+          <t>977; 9571</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>162893; 209508</t>
+          <t>162512; 207627</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5816; 18090</t>
+          <t>6221; 17961</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>201542</t>
+          <t>240246</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>214879</t>
+          <t>267239</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>416421</t>
+          <t>507485</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6359; 19975</t>
+          <t>5532; 20153</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>110703; 155464</t>
+          <t>113238; 158607</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>174960; 229223</t>
+          <t>210429; 270349</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10077; 27060</t>
+          <t>9866; 27783</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>115490; 161868</t>
+          <t>116248; 160433</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>84872; 292670</t>
+          <t>243016; 294093</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19185; 41516</t>
+          <t>19697; 42530</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>240568; 300333</t>
+          <t>240387; 301698</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>262088; 501154</t>
+          <t>468840; 544059</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>18719</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17487</t>
+          <t>25017</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>34300</t>
+          <t>43737</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>14498; 32985</t>
+          <t>14766; 33181</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2051; 12726</t>
+          <t>2100; 12804</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6200; 28746</t>
+          <t>10752; 29817</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8239; 23457</t>
+          <t>9119; 23886</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4013; 16990</t>
+          <t>4214; 16306</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11807; 27242</t>
+          <t>16567; 36987</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26673; 50897</t>
+          <t>25146; 50743</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7699; 23749</t>
+          <t>7622; 23279</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19469; 47893</t>
+          <t>31390; 60300</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>361472</t>
+          <t>434277</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>443825</t>
+          <t>456129</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>805297</t>
+          <t>890406</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>117374; 166824</t>
+          <t>121144; 170593</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>492038; 577072</t>
+          <t>491481; 577793</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>287278; 412953</t>
+          <t>390405; 476922</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>135924; 184531</t>
+          <t>135416; 186417</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>476803; 562513</t>
+          <t>472346; 560787</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>358684; 652698</t>
+          <t>422255; 496250</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>266958; 339684</t>
+          <t>268301; 339356</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>986040; 1118529</t>
+          <t>995617; 1107542</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>703072; 1014943</t>
+          <t>834312; 949008</t>
         </is>
       </c>
     </row>
